--- a/AAII_Financials/Quarterly/RASP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RASP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>RASP</t>
   </si>
@@ -656,136 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -873,8 +880,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,8 +975,14 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1070,14 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1109,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1110,20 +1137,20 @@
       <c r="J12" s="3">
         <v>0</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
+      <c r="O12" s="3">
+        <v>0</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
@@ -1143,8 +1170,8 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V12" s="3">
-        <v>100</v>
+      <c r="V12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>4</v>
@@ -1152,29 +1179,35 @@
       <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
-        <v>0</v>
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
         <v>200</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>300</v>
       </c>
       <c r="AC12" s="3">
         <v>300</v>
       </c>
       <c r="AD12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF12" s="3">
         <v>400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,56 +1295,62 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>2700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1324,11 +1363,11 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1351,8 +1390,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1485,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1521,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1479,88 +1532,94 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3">
         <v>100</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H17" s="3">
         <v>100</v>
       </c>
       <c r="I17" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
       </c>
       <c r="K17" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="L17" s="3">
         <v>100</v>
       </c>
       <c r="M17" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
+        <v>100</v>
+      </c>
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,88 +1627,94 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="H18" s="3">
         <v>-100</v>
       </c>
       <c r="I18" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
       </c>
       <c r="K18" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L18" s="3">
         <v>-100</v>
       </c>
       <c r="M18" s="3">
+        <v>100</v>
+      </c>
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1746,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1690,47 +1757,47 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1770,97 +1837,109 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3">
-        <v>-4000</v>
+      <c r="E21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F21" s="3">
         <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>800</v>
+        <v>-4000</v>
       </c>
       <c r="H21" s="3">
         <v>-100</v>
       </c>
       <c r="I21" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="J21" s="3">
         <v>-100</v>
       </c>
       <c r="K21" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L21" s="3">
         <v>-100</v>
       </c>
       <c r="M21" s="3">
+        <v>100</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1874,29 +1953,29 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1915,26 +1994,26 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1948,8 +2027,14 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1957,96 +2042,102 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
-        <v>-4100</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="3">
         <v>-100</v>
       </c>
       <c r="G23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-100</v>
       </c>
       <c r="M23" s="3">
         <v>-300</v>
       </c>
       <c r="N23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-100</v>
       </c>
       <c r="T23" s="3">
         <v>-200</v>
       </c>
       <c r="U23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -2102,17 +2193,17 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2126,8 +2217,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,8 +2312,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2224,88 +2327,94 @@
         <v>-100</v>
       </c>
       <c r="E26" s="3">
-        <v>-4100</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="3">
         <v>-100</v>
       </c>
       <c r="G26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-100</v>
       </c>
       <c r="M26" s="3">
         <v>-300</v>
       </c>
       <c r="N26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-100</v>
       </c>
       <c r="T26" s="3">
         <v>-200</v>
       </c>
       <c r="U26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2313,88 +2422,94 @@
         <v>-100</v>
       </c>
       <c r="E27" s="3">
-        <v>-4100</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="3">
         <v>-100</v>
       </c>
       <c r="G27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-100</v>
       </c>
       <c r="M27" s="3">
         <v>-300</v>
       </c>
       <c r="N27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-100</v>
       </c>
       <c r="T27" s="3">
         <v>-200</v>
       </c>
       <c r="U27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2535,11 +2656,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>4</v>
@@ -2553,14 +2674,14 @@
       <c r="Y29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>4</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>4</v>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2882,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2758,47 +2897,47 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2838,8 +2977,14 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2847,88 +2992,94 @@
         <v>-100</v>
       </c>
       <c r="E33" s="3">
-        <v>-4100</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="3">
         <v>-100</v>
       </c>
       <c r="G33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-100</v>
       </c>
       <c r="M33" s="3">
         <v>-300</v>
       </c>
       <c r="N33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-100</v>
       </c>
       <c r="T33" s="3">
         <v>-200</v>
       </c>
       <c r="U33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,8 +3167,14 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3025,182 +3182,194 @@
         <v>-100</v>
       </c>
       <c r="E35" s="3">
-        <v>-4100</v>
+        <v>-100</v>
       </c>
       <c r="F35" s="3">
         <v>-100</v>
       </c>
       <c r="G35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-100</v>
       </c>
       <c r="M35" s="3">
         <v>-300</v>
       </c>
       <c r="N35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-100</v>
       </c>
       <c r="T35" s="3">
         <v>-200</v>
       </c>
       <c r="U35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3436,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3274,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -3295,14 +3468,14 @@
         <v>0</v>
       </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
@@ -3316,13 +3489,13 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>100</v>
-      </c>
-      <c r="T41" s="3">
-        <v>100</v>
-      </c>
-      <c r="U41" s="3">
-        <v>0</v>
       </c>
       <c r="V41" s="3">
         <v>100</v>
@@ -3331,31 +3504,37 @@
         <v>0</v>
       </c>
       <c r="X41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>4900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3622,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3500,40 +3685,46 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>100</v>
-      </c>
-      <c r="V43" s="3">
-        <v>100</v>
-      </c>
-      <c r="W43" s="3">
-        <v>200</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
       </c>
       <c r="Y43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>100</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3812,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3630,23 +3827,23 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
@@ -3654,26 +3851,26 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
       <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
@@ -3681,25 +3878,25 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
-      </c>
-      <c r="X45" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>200</v>
       </c>
       <c r="Z45" s="3">
         <v>200</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC45" s="3">
         <v>100</v>
@@ -3707,11 +3904,17 @@
       <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3722,7 +3925,7 @@
         <v>100</v>
       </c>
       <c r="F46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G46" s="3">
         <v>100</v>
@@ -3731,76 +3934,82 @@
         <v>100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
       </c>
       <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3">
         <v>100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3">
         <v>100</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>100</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
       </c>
       <c r="S46" s="3">
         <v>100</v>
       </c>
       <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
+        <v>100</v>
+      </c>
+      <c r="W46" s="3">
         <v>200</v>
-      </c>
-      <c r="V46" s="3">
-        <v>300</v>
-      </c>
-      <c r="W46" s="3">
-        <v>300</v>
       </c>
       <c r="X46" s="3">
         <v>300</v>
       </c>
       <c r="Y46" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA46" s="3">
         <v>700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>4200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>5000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +4097,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3930,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3">
         <v>200</v>
@@ -3969,16 +4184,22 @@
         <v>200</v>
       </c>
       <c r="AC48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4019,13 +4240,13 @@
         <v>0</v>
       </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>4600</v>
-      </c>
-      <c r="R49" s="3">
-        <v>4600</v>
       </c>
       <c r="S49" s="3">
         <v>4600</v>
@@ -4058,16 +4279,22 @@
         <v>4600</v>
       </c>
       <c r="AC49" s="3">
-        <v>4900</v>
+        <v>4600</v>
       </c>
       <c r="AD49" s="3">
-        <v>4900</v>
+        <v>4600</v>
       </c>
       <c r="AE49" s="3">
         <v>4900</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4477,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4333,8 +4572,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4667,14 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4434,7 +4685,7 @@
         <v>100</v>
       </c>
       <c r="F54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G54" s="3">
         <v>100</v>
@@ -4443,76 +4694,82 @@
         <v>100</v>
       </c>
       <c r="I54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K54" s="3">
         <v>0</v>
       </c>
       <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3">
         <v>100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>100</v>
       </c>
-      <c r="N54" s="3">
-        <v>0</v>
-      </c>
-      <c r="O54" s="3">
-        <v>0</v>
-      </c>
       <c r="P54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>0</v>
+      </c>
+      <c r="R54" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>4900</v>
-      </c>
-      <c r="R54" s="3">
-        <v>4900</v>
       </c>
       <c r="S54" s="3">
         <v>4900</v>
       </c>
       <c r="T54" s="3">
+        <v>4900</v>
+      </c>
+      <c r="U54" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V54" s="3">
         <v>5000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5000</v>
-      </c>
-      <c r="V54" s="3">
-        <v>5200</v>
-      </c>
-      <c r="W54" s="3">
-        <v>5200</v>
       </c>
       <c r="X54" s="3">
         <v>5200</v>
       </c>
       <c r="Y54" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Z54" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AA54" s="3">
         <v>5600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>6400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>8300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>9100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>10000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,97 +4836,105 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2100</v>
-      </c>
-      <c r="S57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="T57" s="3">
-        <v>2200</v>
       </c>
       <c r="U57" s="3">
         <v>1400</v>
       </c>
       <c r="V57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4678,65 +4945,65 @@
         <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
       </c>
       <c r="I58" s="3">
+        <v>100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>100</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
-      </c>
-      <c r="O58" s="3">
-        <v>500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>500</v>
       </c>
       <c r="Q58" s="3">
         <v>500</v>
       </c>
       <c r="R58" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="S58" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="T58" s="3">
         <v>300</v>
       </c>
       <c r="U58" s="3">
+        <v>300</v>
+      </c>
+      <c r="V58" s="3">
+        <v>300</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4746,17 +5013,23 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4764,138 +5037,144 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
-      </c>
-      <c r="O60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="P60" s="3">
-        <v>2600</v>
       </c>
       <c r="Q60" s="3">
         <v>2700</v>
       </c>
       <c r="R60" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="S60" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="T60" s="3">
         <v>2500</v>
@@ -4904,37 +5183,43 @@
         <v>2400</v>
       </c>
       <c r="V60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="W60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X60" s="3">
         <v>2300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>1600</v>
       </c>
       <c r="AC60" s="3">
         <v>1500</v>
       </c>
       <c r="AD60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF60" s="3">
         <v>4200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4945,17 +5230,17 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5307,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5060,14 +5351,14 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -5078,32 +5369,32 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
+      <c r="AC62" s="3">
+        <v>0</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
@@ -5111,8 +5402,14 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,58 +5687,64 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F66" s="3">
         <v>2000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1900</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1800</v>
       </c>
       <c r="H66" s="3">
         <v>1900</v>
       </c>
       <c r="I66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K66" s="3">
         <v>2200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2800</v>
-      </c>
-      <c r="O66" s="3">
-        <v>2700</v>
-      </c>
-      <c r="P66" s="3">
-        <v>2600</v>
       </c>
       <c r="Q66" s="3">
         <v>2700</v>
       </c>
       <c r="R66" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="S66" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="T66" s="3">
         <v>2500</v>
@@ -5438,37 +5753,43 @@
         <v>2400</v>
       </c>
       <c r="V66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="W66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X66" s="3">
         <v>2300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>1600</v>
       </c>
       <c r="AC66" s="3">
         <v>1500</v>
       </c>
       <c r="AD66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AE66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF66" s="3">
         <v>4200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6197,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-28600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-28500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-24400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-24200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-24200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-23500</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-23800</v>
       </c>
       <c r="K72" s="3">
         <v>-23500</v>
       </c>
       <c r="L72" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="M72" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="N72" s="3">
         <v>-23200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-23100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-22800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-22700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-17700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-17500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-17300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-17300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-17000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-16800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-16400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-14300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6577,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G76" s="3">
         <v>-1900</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-1700</v>
       </c>
       <c r="H76" s="3">
         <v>-1800</v>
       </c>
       <c r="I76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K76" s="3">
         <v>-2100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-2500</v>
-      </c>
-      <c r="K76" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-2900</v>
       </c>
       <c r="M76" s="3">
         <v>-2800</v>
       </c>
       <c r="N76" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="O76" s="3">
         <v>-2800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Q76" s="3">
         <v>-2700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>6000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>6700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>7600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,102 +6767,114 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6493,88 +6882,94 @@
         <v>-100</v>
       </c>
       <c r="E81" s="3">
-        <v>-4100</v>
+        <v>-100</v>
       </c>
       <c r="F81" s="3">
         <v>-100</v>
       </c>
       <c r="G81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-100</v>
       </c>
       <c r="M81" s="3">
         <v>-300</v>
       </c>
       <c r="N81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-100</v>
       </c>
       <c r="T81" s="3">
         <v>-200</v>
       </c>
       <c r="U81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7001,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6686,17 +7083,23 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7567,14 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7155,25 +7588,25 @@
         <v>0</v>
       </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
       </c>
       <c r="L89" s="3">
         <v>-100</v>
       </c>
       <c r="M89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
@@ -7182,55 +7615,61 @@
         <v>-100</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q89" s="3">
         <v>-100</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-800</v>
       </c>
       <c r="AD89" s="3">
         <v>-800</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7701,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7792,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7982,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7600,14 +8059,14 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7615,11 +8074,17 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8207,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8492,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8016,88 +8507,94 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
       </c>
       <c r="L100" s="3">
         <v>100</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>600</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8176,25 +8673,31 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
@@ -8251,27 +8754,33 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-1300</v>
       </c>
       <c r="AA102" s="3">
         <v>-700</v>
       </c>
       <c r="AB102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RASP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RASP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>RASP</t>
   </si>
@@ -656,143 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -886,8 +890,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1143,17 +1157,17 @@
       <c r="L12" s="3">
         <v>0</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
+      <c r="M12" s="3">
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>4</v>
@@ -1176,23 +1190,23 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="3">
         <v>100</v>
       </c>
-      <c r="AA12" s="3">
-        <v>0</v>
-      </c>
       <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3">
         <v>200</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>300</v>
       </c>
       <c r="AD12" s="3">
         <v>300</v>
@@ -1201,13 +1215,16 @@
         <v>300</v>
       </c>
       <c r="AF12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG12" s="3">
         <v>400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,16 +1318,19 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1318,42 +1338,42 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>2100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1369,8 +1389,8 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,8 +1549,9 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1532,94 +1559,97 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-100</v>
-      </c>
-      <c r="N17" s="3">
-        <v>100</v>
       </c>
       <c r="O17" s="3">
         <v>100</v>
       </c>
       <c r="P17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
-      </c>
-      <c r="T17" s="3">
-        <v>100</v>
       </c>
       <c r="U17" s="3">
         <v>100</v>
       </c>
       <c r="V17" s="3">
+        <v>100</v>
+      </c>
+      <c r="W17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>300</v>
-      </c>
-      <c r="X17" s="3">
-        <v>400</v>
       </c>
       <c r="Y17" s="3">
         <v>400</v>
       </c>
       <c r="Z17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1627,94 +1657,97 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
       </c>
       <c r="P18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-100</v>
       </c>
       <c r="U18" s="3">
         <v>-100</v>
       </c>
       <c r="V18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-300</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-400</v>
       </c>
       <c r="Y18" s="3">
         <v>-400</v>
       </c>
       <c r="Z18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1757,11 +1791,11 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1769,38 +1803,38 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1843,8 +1877,11 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1854,92 +1891,95 @@
       <c r="E21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-100</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-200</v>
       </c>
       <c r="P21" s="3">
         <v>-200</v>
       </c>
       <c r="Q21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R21" s="3">
         <v>-2300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-100</v>
       </c>
       <c r="U21" s="3">
         <v>-100</v>
       </c>
       <c r="V21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-300</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-400</v>
       </c>
       <c r="Y21" s="3">
         <v>-400</v>
       </c>
       <c r="Z21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1947,38 +1987,38 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -2000,23 +2040,23 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2033,8 +2073,11 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2048,88 +2091,91 @@
         <v>-100</v>
       </c>
       <c r="G23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H23" s="3">
         <v>-4100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-100</v>
       </c>
       <c r="I23" s="3">
         <v>-100</v>
       </c>
       <c r="J23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-300</v>
       </c>
       <c r="M23" s="3">
         <v>-300</v>
       </c>
       <c r="N23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2700</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-200</v>
       </c>
       <c r="T23" s="3">
         <v>-200</v>
       </c>
       <c r="U23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-400</v>
       </c>
       <c r="Y23" s="3">
         <v>-400</v>
       </c>
       <c r="Z23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2199,14 +2245,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,8 +2367,11 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2333,88 +2385,91 @@
         <v>-100</v>
       </c>
       <c r="G26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H26" s="3">
         <v>-4100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-100</v>
       </c>
       <c r="I26" s="3">
         <v>-100</v>
       </c>
       <c r="J26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-300</v>
       </c>
       <c r="M26" s="3">
         <v>-300</v>
       </c>
       <c r="N26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2700</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-200</v>
       </c>
       <c r="T26" s="3">
         <v>-200</v>
       </c>
       <c r="U26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-400</v>
       </c>
       <c r="Y26" s="3">
         <v>-400</v>
       </c>
       <c r="Z26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2428,88 +2483,91 @@
         <v>-100</v>
       </c>
       <c r="G27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H27" s="3">
         <v>-4100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-100</v>
       </c>
       <c r="I27" s="3">
         <v>-100</v>
       </c>
       <c r="J27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>300</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-300</v>
       </c>
       <c r="M27" s="3">
         <v>-300</v>
       </c>
       <c r="N27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2700</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-200</v>
       </c>
       <c r="T27" s="3">
         <v>-200</v>
       </c>
       <c r="U27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-400</v>
       </c>
       <c r="Y27" s="3">
         <v>-400</v>
       </c>
       <c r="Z27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2662,8 +2723,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>4</v>
@@ -2680,11 +2741,11 @@
       <c r="AA29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>4</v>
+      <c r="AB29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>4</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2897,11 +2967,11 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2909,38 +2979,38 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2983,8 +3053,11 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2998,88 +3071,91 @@
         <v>-100</v>
       </c>
       <c r="G33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H33" s="3">
         <v>-4100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-100</v>
       </c>
       <c r="I33" s="3">
         <v>-100</v>
       </c>
       <c r="J33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>300</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-300</v>
       </c>
       <c r="M33" s="3">
         <v>-300</v>
       </c>
       <c r="N33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2700</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-200</v>
       </c>
       <c r="T33" s="3">
         <v>-200</v>
       </c>
       <c r="U33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-400</v>
       </c>
       <c r="Y33" s="3">
         <v>-400</v>
       </c>
       <c r="Z33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,8 +3249,11 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3188,188 +3267,194 @@
         <v>-100</v>
       </c>
       <c r="G35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H35" s="3">
         <v>-4100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-100</v>
       </c>
       <c r="I35" s="3">
         <v>-100</v>
       </c>
       <c r="J35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>300</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-300</v>
       </c>
       <c r="M35" s="3">
         <v>-300</v>
       </c>
       <c r="N35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2700</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-200</v>
       </c>
       <c r="T35" s="3">
         <v>-200</v>
       </c>
       <c r="U35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-400</v>
       </c>
       <c r="Y35" s="3">
         <v>-400</v>
       </c>
       <c r="Z35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,8 +3524,9 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3447,11 +3534,11 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
         <v>0</v>
       </c>
@@ -3474,11 +3561,11 @@
         <v>0</v>
       </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
@@ -3495,46 +3582,49 @@
         <v>0</v>
       </c>
       <c r="U41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V41" s="3">
         <v>100</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
         <v>0</v>
       </c>
       <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3691,20 +3784,20 @@
         <v>0</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
       </c>
       <c r="Y43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
@@ -3712,19 +3805,22 @@
         <v>0</v>
       </c>
       <c r="AD43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="3">
         <v>100</v>
       </c>
       <c r="AF43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3833,20 +3932,20 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -3857,11 +3956,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3869,11 +3968,11 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
@@ -3884,13 +3983,13 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>200</v>
@@ -3899,7 +3998,7 @@
         <v>200</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD45" s="3">
         <v>100</v>
@@ -3910,11 +4009,14 @@
       <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3922,13 +4024,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
         <v>100</v>
       </c>
-      <c r="F46" s="3">
-        <v>0</v>
-      </c>
       <c r="G46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3">
         <v>100</v>
@@ -3940,7 +4042,7 @@
         <v>100</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -3949,37 +4051,37 @@
         <v>0</v>
       </c>
       <c r="N46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O46" s="3">
         <v>100</v>
       </c>
       <c r="P46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S46" s="3">
         <v>100</v>
       </c>
       <c r="T46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V46" s="3">
         <v>100</v>
       </c>
       <c r="W46" s="3">
+        <v>100</v>
+      </c>
+      <c r="X46" s="3">
         <v>200</v>
-      </c>
-      <c r="X46" s="3">
-        <v>300</v>
       </c>
       <c r="Y46" s="3">
         <v>300</v>
@@ -3988,28 +4090,31 @@
         <v>300</v>
       </c>
       <c r="AA46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB46" s="3">
         <v>700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4151,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>200</v>
@@ -4190,16 +4298,19 @@
         <v>200</v>
       </c>
       <c r="AE48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
+        <v>200</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>0</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4246,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
         <v>1900</v>
-      </c>
-      <c r="S49" s="3">
-        <v>4600</v>
       </c>
       <c r="T49" s="3">
         <v>4600</v>
@@ -4285,7 +4396,7 @@
         <v>4600</v>
       </c>
       <c r="AE49" s="3">
-        <v>4900</v>
+        <v>4600</v>
       </c>
       <c r="AF49" s="3">
         <v>4900</v>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>4900</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,8 +4796,11 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4682,13 +4808,13 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3">
         <v>100</v>
       </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
       <c r="G54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H54" s="3">
         <v>100</v>
@@ -4700,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="K54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -4709,22 +4835,22 @@
         <v>0</v>
       </c>
       <c r="N54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O54" s="3">
         <v>100</v>
       </c>
       <c r="P54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q54" s="3">
         <v>0</v>
       </c>
       <c r="R54" s="3">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3">
         <v>2200</v>
-      </c>
-      <c r="S54" s="3">
-        <v>4900</v>
       </c>
       <c r="T54" s="3">
         <v>4900</v>
@@ -4733,13 +4859,13 @@
         <v>4900</v>
       </c>
       <c r="V54" s="3">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="W54" s="3">
         <v>5000</v>
       </c>
       <c r="X54" s="3">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="Y54" s="3">
         <v>5200</v>
@@ -4748,28 +4874,31 @@
         <v>5200</v>
       </c>
       <c r="AA54" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AB54" s="3">
         <v>5600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4847,99 +4978,102 @@
         <v>1900</v>
       </c>
       <c r="E57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2100</v>
       </c>
       <c r="M57" s="3">
         <v>2100</v>
       </c>
       <c r="N57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O57" s="3">
         <v>2200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>2300</v>
       </c>
       <c r="P57" s="3">
         <v>2300</v>
       </c>
       <c r="Q57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R57" s="3">
         <v>1500</v>
-      </c>
-      <c r="R57" s="3">
-        <v>2200</v>
       </c>
       <c r="S57" s="3">
         <v>2200</v>
       </c>
       <c r="T57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U57" s="3">
         <v>2100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2200</v>
-      </c>
-      <c r="W57" s="3">
-        <v>1400</v>
       </c>
       <c r="X57" s="3">
         <v>1400</v>
       </c>
       <c r="Y57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>200</v>
@@ -4951,7 +5085,7 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>100</v>
@@ -4960,25 +5094,25 @@
         <v>100</v>
       </c>
       <c r="K58" s="3">
+        <v>100</v>
+      </c>
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
-      </c>
-      <c r="O58" s="3">
-        <v>600</v>
       </c>
       <c r="P58" s="3">
         <v>600</v>
       </c>
       <c r="Q58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="R58" s="3">
         <v>500</v>
@@ -4987,7 +5121,7 @@
         <v>500</v>
       </c>
       <c r="T58" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="U58" s="3">
         <v>300</v>
@@ -4996,17 +5130,17 @@
         <v>300</v>
       </c>
       <c r="W58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X58" s="3">
         <v>200</v>
       </c>
       <c r="Y58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z58" s="3">
         <v>100</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5019,8 +5153,8 @@
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -5028,8 +5162,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5037,11 +5174,11 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
       <c r="G59" s="3">
         <v>0</v>
       </c>
@@ -5049,22 +5186,22 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
       <c r="K59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
       </c>
       <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
@@ -5072,154 +5209,160 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>800</v>
-      </c>
-      <c r="X59" s="3">
-        <v>700</v>
       </c>
       <c r="Y59" s="3">
         <v>700</v>
       </c>
       <c r="Z59" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA59" s="3">
         <v>600</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>400</v>
       </c>
       <c r="AB59" s="3">
         <v>400</v>
       </c>
       <c r="AC59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD59" s="3">
         <v>300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>500</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG59" s="3">
         <v>2600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E60" s="3">
         <v>2100</v>
       </c>
       <c r="F60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5236,13 +5379,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5313,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5357,11 +5503,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -5375,17 +5521,17 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
+      <c r="Z62" s="3">
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
@@ -5393,11 +5539,11 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E66" s="3">
         <v>2100</v>
       </c>
       <c r="F66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G66" s="3">
         <v>2000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1900</v>
       </c>
       <c r="H66" s="3">
         <v>1900</v>
       </c>
       <c r="I66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-28800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-24400</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-24200</v>
       </c>
       <c r="J72" s="3">
         <v>-24200</v>
       </c>
       <c r="K72" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="L72" s="3">
         <v>-23500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-23800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-23200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-23100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-22700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-20400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-17500</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-17300</v>
       </c>
       <c r="V72" s="3">
         <v>-17300</v>
       </c>
       <c r="W72" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="X72" s="3">
         <v>-17000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-16800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-12300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-10500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>-2000</v>
       </c>
       <c r="F76" s="3">
         <v>-2000</v>
       </c>
       <c r="G76" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H76" s="3">
         <v>-1900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-2100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-2500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-2800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-2800</v>
       </c>
       <c r="P76" s="3">
         <v>-2800</v>
       </c>
       <c r="Q76" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="R76" s="3">
         <v>-2700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2400</v>
-      </c>
-      <c r="U76" s="3">
-        <v>2500</v>
       </c>
       <c r="V76" s="3">
         <v>2500</v>
       </c>
       <c r="W76" s="3">
+        <v>2500</v>
+      </c>
+      <c r="X76" s="3">
         <v>2700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,108 +6962,114 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6888,88 +7083,91 @@
         <v>-100</v>
       </c>
       <c r="G81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H81" s="3">
         <v>-4100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-100</v>
       </c>
       <c r="I81" s="3">
         <v>-100</v>
       </c>
       <c r="J81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>300</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-300</v>
       </c>
       <c r="M81" s="3">
         <v>-300</v>
       </c>
       <c r="N81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2700</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-200</v>
       </c>
       <c r="T81" s="3">
         <v>-200</v>
       </c>
       <c r="U81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-400</v>
       </c>
       <c r="Y81" s="3">
         <v>-400</v>
       </c>
       <c r="Z81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7089,8 +7288,8 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>4</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,8 +7787,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7594,22 +7811,22 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L89" s="3">
         <v>-100</v>
       </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
         <v>-100</v>
@@ -7621,16 +7838,16 @@
         <v>-100</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T89" s="3">
         <v>-100</v>
       </c>
       <c r="U89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -7639,25 +7856,25 @@
         <v>0</v>
       </c>
       <c r="X89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="3">
         <v>-100</v>
       </c>
       <c r="Z89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-1300</v>
       </c>
       <c r="AC89" s="3">
         <v>-1300</v>
       </c>
       <c r="AD89" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="AE89" s="3">
         <v>-800</v>
@@ -7665,11 +7882,14 @@
       <c r="AF89" s="3">
         <v>-800</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8065,11 +8295,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -8080,11 +8310,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8507,11 +8753,11 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -8519,29 +8765,29 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3">
         <v>100</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -8549,13 +8795,13 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T100" s="3">
         <v>100</v>
       </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8564,13 +8810,13 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
         <v>100</v>
       </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -8579,22 +8825,25 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
+      <c r="AF100" s="3">
+        <v>0</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8679,8 +8928,8 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>4</v>
@@ -8688,20 +8937,23 @@
       <c r="AG101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
@@ -8760,27 +9012,30 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1200</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
